--- a/docs/obosnovanie2025/Опись_приложений_шаблон.xlsx
+++ b/docs/obosnovanie2025/Опись_приложений_шаблон.xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H89"/>
+  <dimension ref="A2:I89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="30" min="1" max="1"/>
@@ -790,7 +790,7 @@
     <row r="7" ht="15" customHeight="1" s="31">
       <c r="B7" s="37" t="inlineStr">
         <is>
-          <t>Заполняйте колонки B–G. № п/п (A) и Приложение № (B) рассчитываются автоматически — НЕ редактируйте формулы в столбцах A и H.</t>
+          <t>Заполняйте колонки B–G. № п/п (A) и Приложение № (B) рассчитываются автоматически — НЕ редактируйте формулы в столбцах A и H Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории).</t>
         </is>
       </c>
     </row>
@@ -834,6 +834,11 @@
       <c r="H9" s="38" t="inlineStr">
         <is>
           <t>Приложение №</t>
+        </is>
+      </c>
+      <c r="I9" s="30" t="inlineStr">
+        <is>
+          <t>Ссылка Яндекс.Диск</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1688,7 @@
       </c>
       <c r="C34" s="40" t="inlineStr">
         <is>
-          <t>Поставщики (архив частями .001–.009)</t>
+          <t>(заменено строкой 11.1 — Яндекс.Диск)</t>
         </is>
       </c>
       <c r="D34" s="41" t="n">
@@ -1691,20 +1696,27 @@
       </c>
       <c r="E34" s="42" t="inlineStr">
         <is>
-          <t>части .001–.009</t>
-        </is>
-      </c>
-      <c r="F34" s="43" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G34" s="44" t="inlineStr">
         <is>
-          <t>11.1_Поставщики.zip.001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H34" s="45">
         <f>IF(B34="","",LEFT(B34,2)&amp;"."&amp;COUNTIF($B$10:B34,B34))</f>
         <v/>
+      </c>
+      <c r="I34" s="30" t="inlineStr">
+        <is>
+          <t>см. прил. 11.1</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="27.75" customHeight="1" s="31">
@@ -1712,15 +1724,40 @@
         <f>IF(C35="","",COUNTA($C$10:C35))</f>
         <v/>
       </c>
-      <c r="B35" s="40" t="n"/>
-      <c r="C35" s="40" t="n"/>
-      <c r="D35" s="41" t="n"/>
-      <c r="E35" s="42" t="n"/>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="44" t="n"/>
+      <c r="B35" s="40" t="inlineStr">
+        <is>
+          <t>12 Разнарядки</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>Сводная ведомость разнарядок соцтакси за 2024 год</t>
+        </is>
+      </c>
+      <c r="D35" s="41" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E35" s="42" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="F35" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" s="44" t="inlineStr">
+        <is>
+          <t>12.1_Сводная_ведомость_разнарядок_2024.xlsx</t>
+        </is>
+      </c>
       <c r="H35" s="45">
         <f>IF(B35="","",LEFT(B35,2)&amp;"."&amp;COUNTIF($B$10:B35,B35))</f>
         <v/>
+      </c>
+      <c r="I35" s="30" t="inlineStr">
+        <is>
+          <t>исходники PDF: приложение 12.3 (Яндекс.Диск)</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="27.75" customHeight="1" s="31">
@@ -1728,15 +1765,40 @@
         <f>IF(C36="","",COUNTA($C$10:C36))</f>
         <v/>
       </c>
-      <c r="B36" s="40" t="n"/>
-      <c r="C36" s="40" t="n"/>
-      <c r="D36" s="41" t="n"/>
-      <c r="E36" s="42" t="n"/>
-      <c r="F36" s="43" t="n"/>
-      <c r="G36" s="44" t="n"/>
+      <c r="B36" s="40" t="inlineStr">
+        <is>
+          <t>12 Разнарядки</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="inlineStr">
+        <is>
+          <t>Сводная ведомость разнарядок соцтакси за 2025 год</t>
+        </is>
+      </c>
+      <c r="D36" s="41" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E36" s="42" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="F36" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" s="44" t="inlineStr">
+        <is>
+          <t>12.2_Сводная_ведомость_разнарядок_2025.xlsx</t>
+        </is>
+      </c>
       <c r="H36" s="45">
         <f>IF(B36="","",LEFT(B36,2)&amp;"."&amp;COUNTIF($B$10:B36,B36))</f>
         <v/>
+      </c>
+      <c r="I36" s="30" t="inlineStr">
+        <is>
+          <t>исходники PDF: приложение 12.4 (Яндекс.Диск)</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="31">
@@ -1744,15 +1806,40 @@
         <f>IF(C37="","",COUNTA($C$10:C37))</f>
         <v/>
       </c>
-      <c r="B37" s="40" t="n"/>
-      <c r="C37" s="40" t="n"/>
-      <c r="D37" s="41" t="n"/>
-      <c r="E37" s="42" t="n"/>
-      <c r="F37" s="43" t="n"/>
-      <c r="G37" s="44" t="n"/>
+      <c r="B37" s="40" t="inlineStr">
+        <is>
+          <t>11 Поставщики</t>
+        </is>
+      </c>
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>Сводная ведомость поставщиков (реестр папок и предмет договоров)</t>
+        </is>
+      </c>
+      <c r="D37" s="41" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E37" s="42" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="F37" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="44" t="inlineStr">
+        <is>
+          <t>11.2_Сводная_ведомость_поставщиков.xlsx</t>
+        </is>
+      </c>
       <c r="H37" s="45">
         <f>IF(B37="","",LEFT(B37,2)&amp;"."&amp;COUNTIF($B$10:B37,B37))</f>
         <v/>
+      </c>
+      <c r="I37" s="30" t="inlineStr">
+        <is>
+          <t>исходники PDF: приложение 11.1 (Яндекс.Диск)</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="27.75" customHeight="1" s="31">
@@ -1760,15 +1847,42 @@
         <f>IF(C38="","",COUNTA($C$10:C38))</f>
         <v/>
       </c>
-      <c r="B38" s="40" t="n"/>
-      <c r="C38" s="40" t="n"/>
-      <c r="D38" s="41" t="n"/>
-      <c r="E38" s="42" t="n"/>
-      <c r="F38" s="43" t="n"/>
-      <c r="G38" s="44" t="n"/>
+      <c r="B38" s="40" t="inlineStr">
+        <is>
+          <t>11 Поставщики</t>
+        </is>
+      </c>
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>Архив документов поставщиков (исходные PDF, папки 1–37)</t>
+        </is>
+      </c>
+      <c r="D38" s="41" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E38" s="42" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="F38" s="43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" s="44" t="inlineStr">
+        <is>
+          <t>(только Яндекс.Диск; см. кол. I)</t>
+        </is>
+      </c>
       <c r="H38" s="45">
         <f>IF(B38="","",LEFT(B38,2)&amp;"."&amp;COUNTIF($B$10:B38,B38))</f>
         <v/>
+      </c>
+      <c r="I38" s="30" t="inlineStr">
+        <is>
+          <t>https://disk.yandex.ru/…</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="27.75" customHeight="1" s="31">
@@ -1776,15 +1890,42 @@
         <f>IF(C39="","",COUNTA($C$10:C39))</f>
         <v/>
       </c>
-      <c r="B39" s="40" t="n"/>
-      <c r="C39" s="40" t="n"/>
-      <c r="D39" s="41" t="n"/>
-      <c r="E39" s="42" t="n"/>
-      <c r="F39" s="43" t="n"/>
-      <c r="G39" s="44" t="n"/>
+      <c r="B39" s="40" t="inlineStr">
+        <is>
+          <t>12 Разнарядки</t>
+        </is>
+      </c>
+      <c r="C39" s="40" t="inlineStr">
+        <is>
+          <t>Исходные PDF разнарядок за 2024 год (сканы)</t>
+        </is>
+      </c>
+      <c r="D39" s="41" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E39" s="42" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="F39" s="43" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="G39" s="44" t="inlineStr">
+        <is>
+          <t>(только Яндекс.Диск)</t>
+        </is>
+      </c>
       <c r="H39" s="45">
         <f>IF(B39="","",LEFT(B39,2)&amp;"."&amp;COUNTIF($B$10:B39,B39))</f>
         <v/>
+      </c>
+      <c r="I39" s="30" t="inlineStr">
+        <is>
+          <t>https://disk.yandex.ru/…</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="27.75" customHeight="1" s="31">
@@ -1792,15 +1933,42 @@
         <f>IF(C40="","",COUNTA($C$10:C40))</f>
         <v/>
       </c>
-      <c r="B40" s="40" t="n"/>
-      <c r="C40" s="40" t="n"/>
-      <c r="D40" s="41" t="n"/>
-      <c r="E40" s="42" t="n"/>
-      <c r="F40" s="43" t="n"/>
-      <c r="G40" s="44" t="n"/>
+      <c r="B40" s="40" t="inlineStr">
+        <is>
+          <t>12 Разнарядки</t>
+        </is>
+      </c>
+      <c r="C40" s="40" t="inlineStr">
+        <is>
+          <t>Исходные PDF разнарядок за 2025 год (по дням)</t>
+        </is>
+      </c>
+      <c r="D40" s="41" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E40" s="42" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="F40" s="43" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="G40" s="44" t="inlineStr">
+        <is>
+          <t>(только Яндекс.Диск)</t>
+        </is>
+      </c>
       <c r="H40" s="45">
         <f>IF(B40="","",LEFT(B40,2)&amp;"."&amp;COUNTIF($B$10:B40,B40))</f>
         <v/>
+      </c>
+      <c r="I40" s="30" t="inlineStr">
+        <is>
+          <t>https://disk.yandex.ru/…</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="27.75" customHeight="1" s="31">

--- a/docs/obosnovanie2025/Опись_приложений_шаблон.xlsx
+++ b/docs/obosnovanie2025/Опись_приложений_шаблон.xlsx
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
-          <t>Сводная ведомость разнарядок соцтакси за 2024 год</t>
+          <t>Сводная ведомость PDF разнарядок соцтакси за 2024 год</t>
         </is>
       </c>
       <c r="D35" s="41" t="n">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="F35" s="43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G35" s="44" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C36" s="40" t="inlineStr">
         <is>
-          <t>Сводная ведомость разнарядок соцтакси за 2025 год</t>
+          <t>Сводная ведомость PDF разнарядок соцтакси за 2025 год</t>
         </is>
       </c>
       <c r="D36" s="41" t="n">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="F36" s="43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G36" s="44" t="inlineStr">
         <is>

--- a/docs/obosnovanie2025/Опись_приложений_шаблон.xlsx
+++ b/docs/obosnovanie2025/Опись_приложений_шаблон.xlsx
@@ -790,7 +790,7 @@
     <row r="7" ht="15" customHeight="1" s="31">
       <c r="B7" s="37" t="inlineStr">
         <is>
-          <t>Заполняйте колонки B–G. № п/п (A) и Приложение № (B) рассчитываются автоматически — НЕ редактируйте формулы в столбцах A и H Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории).</t>
+          <t>Заполняйте колонки B–G. № п/п (A) и Приложение № (B) рассчитываются автоматически — НЕ редактируйте формулы в столбцах A и H Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории) Колонка I — публичная ссылка на архив PDF (если файл не в репозитории).</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="I39" s="30" t="inlineStr">
         <is>
-          <t>https://disk.yandex.ru/…</t>
+          <t>https://disk.yandex.ru/d/Jd3vahf13dVBfw</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="I40" s="30" t="inlineStr">
         <is>
-          <t>https://disk.yandex.ru/…</t>
+          <t>https://disk.yandex.ru/d/gKOp4RxwJ72r_w</t>
         </is>
       </c>
     </row>
@@ -1976,15 +1976,42 @@
         <f>IF(C41="","",COUNTA($C$10:C41))</f>
         <v/>
       </c>
-      <c r="B41" s="40" t="n"/>
-      <c r="C41" s="40" t="n"/>
-      <c r="D41" s="41" t="n"/>
-      <c r="E41" s="42" t="n"/>
-      <c r="F41" s="43" t="n"/>
-      <c r="G41" s="44" t="n"/>
+      <c r="B41" s="40" t="inlineStr">
+        <is>
+          <t>13 Путевые листы</t>
+        </is>
+      </c>
+      <c r="C41" s="40" t="inlineStr">
+        <is>
+          <t>Исходные PDF путевых листов за 2024 год</t>
+        </is>
+      </c>
+      <c r="D41" s="41" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E41" s="42" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="F41" s="43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G41" s="44" t="inlineStr">
+        <is>
+          <t>(только Яндекс.Диск; см. кол. I)</t>
+        </is>
+      </c>
       <c r="H41" s="45">
         <f>IF(B41="","",LEFT(B41,2)&amp;"."&amp;COUNTIF($B$10:B41,B41))</f>
         <v/>
+      </c>
+      <c r="I41" s="30" t="inlineStr">
+        <is>
+          <t>https://disk.yandex.ru/…</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="27.75" customHeight="1" s="31">
@@ -1992,15 +2019,40 @@
         <f>IF(C42="","",COUNTA($C$10:C42))</f>
         <v/>
       </c>
-      <c r="B42" s="40" t="n"/>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="41" t="n"/>
-      <c r="E42" s="42" t="n"/>
-      <c r="F42" s="43" t="n"/>
-      <c r="G42" s="44" t="n"/>
+      <c r="B42" s="40" t="inlineStr">
+        <is>
+          <t>13 Путевые листы</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
+          <t>Сводная ведомость путевых листов за 2024 год (PDF)</t>
+        </is>
+      </c>
+      <c r="D42" s="41" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E42" s="42" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="F42" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="44" t="inlineStr">
+        <is>
+          <t>13.2_Сводная_ведомость_путевые_листы_2024.xlsx</t>
+        </is>
+      </c>
       <c r="H42" s="45">
         <f>IF(B42="","",LEFT(B42,2)&amp;"."&amp;COUNTIF($B$10:B42,B42))</f>
         <v/>
+      </c>
+      <c r="I42" s="30" t="inlineStr">
+        <is>
+          <t>исходники PDF: приложение 13.1 (Яндекс.Диск)</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="27.75" customHeight="1" s="31">
